--- a/artfynd/A 39593-2026 artfynd.xlsx
+++ b/artfynd/A 39593-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92541</v>
+        <v>92543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136583148</v>
       </c>
       <c r="B6" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2026 artfynd.xlsx
+++ b/artfynd/A 39593-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136583148</v>
       </c>
       <c r="B6" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2026 artfynd.xlsx
+++ b/artfynd/A 39593-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136583148</v>
       </c>
       <c r="B6" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2026 artfynd.xlsx
+++ b/artfynd/A 39593-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92547</v>
+        <v>92548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136583148</v>
       </c>
       <c r="B6" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2026 artfynd.xlsx
+++ b/artfynd/A 39593-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92548</v>
+        <v>92554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136583148</v>
       </c>
       <c r="B6" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2026 artfynd.xlsx
+++ b/artfynd/A 39593-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92554</v>
+        <v>92558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136583148</v>
       </c>
       <c r="B6" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2026 artfynd.xlsx
+++ b/artfynd/A 39593-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>136583148</v>
       </c>
       <c r="B6" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39593-2026 artfynd.xlsx
+++ b/artfynd/A 39593-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136583149</v>
       </c>
       <c r="B3" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>136583148</v>
       </c>
       <c r="B6" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
